--- a/data/raw/PSY_SUD_comorbidity_prevalence.xlsx
+++ b/data/raw/PSY_SUD_comorbidity_prevalence.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giaco\Desktop\Git_META\META\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AF3860-07CD-4265-87B2-8FF55E1F1DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB2F4D9-A319-4774-AB8D-4F8D7A78FD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>DISORDER</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t>CHR</t>
-  </si>
-  <si>
-    <t>Schizotypic</t>
-  </si>
-  <si>
-    <t>PTSD</t>
   </si>
   <si>
     <t>SUD</t>
@@ -172,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -196,9 +190,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -425,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:S998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" customWidth="1"/>
@@ -434,29 +425,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="98.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -469,19 +460,19 @@
       <c r="C2" s="5">
         <v>16.100000000000001</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>41</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -533,7 +524,7 @@
       <c r="G4" s="6">
         <v>34</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -576,7 +567,7 @@
       <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>30</v>
       </c>
       <c r="F6" s="6">
@@ -682,79 +673,45 @@
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>7.5</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>3.1</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>0.2</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>0.1</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>1.7</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="8" customFormat="1" ht="172.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="12">
-        <v>35</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="8" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="12">
-        <v>39.9</v>
-      </c>
-      <c r="C12" s="4">
-        <v>57.7</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="12">
-        <v>9.4</v>
-      </c>
-      <c r="F12" s="12">
-        <v>42.9</v>
-      </c>
-      <c r="G12" s="12">
-        <v>45.3</v>
-      </c>
-      <c r="H12" s="12">
-        <v>41</v>
-      </c>
+    <row r="11" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
@@ -766,13 +723,13 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
@@ -9630,24 +9587,6 @@
       <c r="G998" s="1"/>
       <c r="H998" s="1"/>
     </row>
-    <row r="999" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B999" s="1"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-      <c r="H999" s="1"/>
-    </row>
-    <row r="1000" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
